--- a/data/leermiddelen-die-keure.xlsx
+++ b/data/leermiddelen-die-keure.xlsx
@@ -1,18 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14CC9B3-7D36-164E-A97A-466BE3FD8A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A1FE6C-856E-4CFC-A2E6-BE13A8FAAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leermiddel" sheetId="4" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -152,7 +149,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,8 +164,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -180,14 +185,8 @@
         <fgColor rgb="FFE0E0E0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -195,22 +194,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -219,18 +207,484 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -243,34 +697,36 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Organisatie"/>
-      <sheetName val="Collectie"/>
-      <sheetName val="Leerplan"/>
-      <sheetName val="Niveau"/>
-      <sheetName val="Onderwerp"/>
-      <sheetName val="Doel"/>
-      <sheetName val="Leermiddel"/>
-      <sheetName val="_relaties"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{066E2D8D-1858-4260-9449-755DF9C432CA}" name="Table1" displayName="Table1" ref="A1:U5" totalsRowShown="0" headerRowDxfId="22" dataDxfId="0">
+  <autoFilter ref="A1:U5" xr:uid="{066E2D8D-1858-4260-9449-755DF9C432CA}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{EE5AE287-BBE7-4EDC-9879-889396EA54B0}" name="CODE" dataDxfId="21">
+      <calculatedColumnFormula array="1">LOWER(LEFT(SUBSTITUTE(Table1[[#This Row],[naam]]," ","-"), 24) &amp; "-" &amp; RIGHT(DEC2HEX(ABS(SUMPRODUCT(CODE(MID(Table1[[#This Row],[naam]],ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))),1))*(ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))))))), 4))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{27AD3527-329E-4436-A20C-8D57E5811B88}" name="beschrijving" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{685534C3-F251-4B1A-9934-50C0AD0A2947}" name="instructie" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{AEA5F394-85C3-4C52-8B3E-DCED8A6EB745}" name="naam" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{DC53031F-BBDF-4EA6-B0DD-8F9950485C6E}" name="vereiste" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{8760A467-302E-45F6-92FF-BE55B379434E}" name="benodigdMateriaal" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{67E7A6E0-67F1-496B-B8DB-441E8DAC2C68}" name="sleutelwoord" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{50896DBB-E1AD-4329-9559-0B4FE2F422D9}" name="onderwerp" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{DF466037-E445-4D23-B006-D06BF5EB45F8}" name="toegankelijkheid" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{0E1F9F7A-A2F8-49AF-A2FE-FF5059D90229}" name="type" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{2D12D7BC-B459-454C-B336-A785D5A2A725}" name="interactieType" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{B38D423A-C574-45ED-B7BA-46D5798944C6}" name="instructietaal" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{ECA5028B-A00D-4EB2-A30D-8E9590701542}" name="resultaat" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{419FA497-E252-440D-A843-38DF4E8BD901}" name="niveau" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{57CAC6A4-E015-4965-B56A-CFB760540DE6}" name="kost" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{2924354C-3D9D-4634-980A-AE5127D37AB0}" name="formaat" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{B0E9C66A-1627-4905-803E-0A2F364BB97E}" name="competentie" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{36E406D4-1A0F-4F14-84C3-54DA1F81C7AE}" name="bron" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{26FC4A58-7357-4ADA-A6DC-63F02BF1348F}" name="dient" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{A9422CE0-02F3-4C9A-8861-799F58D30F7B}" name="isLidVan" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{C1EF498E-6C63-4AC8-9E91-0FD939D87DF0}" name="bestaatUit" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -596,198 +1052,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="40" style="1" customWidth="1"/>
-    <col min="15" max="15" width="4.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" t="str" cm="1">
-        <f t="array" aca="1" ref="A2" ca="1">LOWER(LEFT(SUBSTITUTE([1]!Table7[[#This Row],[naam]]," ","-"), 24) &amp; "-" &amp; RIGHT(DEC2HEX(ABS(SUMPRODUCT(CODE(MID([1]!Table7[[#This Row],[naam]],ROW(INDIRECT("1:"&amp;LEN([1]!Table7[[#This Row],[naam]]))),1))*(ROW(INDIRECT("1:"&amp;LEN([1]!Table7[[#This Row],[naam]]))))))), 4))</f>
-        <v>isaac-natuurwetenschappe-90c6</v>
-      </c>
+    <row r="2" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="str" cm="1">
+        <f t="array" aca="1" ref="A2" ca="1">LOWER(LEFT(SUBSTITUTE(Table1[[#This Row],[naam]]," ","-"), 24) &amp; "-" &amp; RIGHT(DEC2HEX(ABS(SUMPRODUCT(CODE(MID(Table1[[#This Row],[naam]],ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))),1))*(ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))))))), 4))</f>
+        <v>janus-3-d-bf2</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
       <c r="R2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="str" cm="1">
-        <f t="array" aca="1" ref="A3" ca="1">LOWER(LEFT(SUBSTITUTE([1]!Table7[[#This Row],[naam]]," ","-"), 24) &amp; "-" &amp; RIGHT(DEC2HEX(ABS(SUMPRODUCT(CODE(MID([1]!Table7[[#This Row],[naam]],ROW(INDIRECT("1:"&amp;LEN([1]!Table7[[#This Row],[naam]]))),1))*(ROW(INDIRECT("1:"&amp;LEN([1]!Table7[[#This Row],[naam]]))))))), 4))</f>
-        <v>isaac-natuurwetenschappe-976e</v>
-      </c>
-      <c r="D3" s="5" t="s">
+    <row r="3" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="str" cm="1">
+        <f t="array" aca="1" ref="A3" ca="1">LOWER(LEFT(SUBSTITUTE(Table1[[#This Row],[naam]]," ","-"), 24) &amp; "-" &amp; RIGHT(DEC2HEX(ABS(SUMPRODUCT(CODE(MID(Table1[[#This Row],[naam]],ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))),1))*(ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))))))), 4))</f>
+        <v>janus-3-d&amp;a-1039</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="M3" s="4"/>
+      <c r="N3" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
       <c r="R3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="5"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" t="str" cm="1">
-        <f t="array" aca="1" ref="A4" ca="1">LOWER(LEFT(SUBSTITUTE([1]!Table7[[#This Row],[naam]]," ","-"), 24) &amp; "-" &amp; RIGHT(DEC2HEX(ABS(SUMPRODUCT(CODE(MID([1]!Table7[[#This Row],[naam]],ROW(INDIRECT("1:"&amp;LEN([1]!Table7[[#This Row],[naam]]))),1))*(ROW(INDIRECT("1:"&amp;LEN([1]!Table7[[#This Row],[naam]]))))))), 4))</f>
-        <v>max-natuur-1b-1e02</v>
-      </c>
+    <row r="4" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="str" cm="1">
+        <f t="array" aca="1" ref="A4" ca="1">LOWER(LEFT(SUBSTITUTE(Table1[[#This Row],[naam]]," ","-"), 24) &amp; "-" &amp; RIGHT(DEC2HEX(ABS(SUMPRODUCT(CODE(MID(Table1[[#This Row],[naam]],ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))),1))*(ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))))))), 4))</f>
+        <v>janus-4-d-bf9</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="M4" s="4"/>
       <c r="N4" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
       <c r="R4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="str" cm="1">
-        <f t="array" aca="1" ref="A5" ca="1">LOWER(LEFT(SUBSTITUTE([1]!Table7[[#This Row],[naam]]," ","-"), 24) &amp; "-" &amp; RIGHT(DEC2HEX(ABS(SUMPRODUCT(CODE(MID([1]!Table7[[#This Row],[naam]],ROW(INDIRECT("1:"&amp;LEN([1]!Table7[[#This Row],[naam]]))),1))*(ROW(INDIRECT("1:"&amp;LEN([1]!Table7[[#This Row],[naam]]))))))), 4))</f>
-        <v>max-natuur-2b-1e0e</v>
-      </c>
-      <c r="D5" s="5" t="s">
+    <row r="5" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="str" cm="1">
+        <f t="array" aca="1" ref="A5" ca="1">LOWER(LEFT(SUBSTITUTE(Table1[[#This Row],[naam]]," ","-"), 24) &amp; "-" &amp; RIGHT(DEC2HEX(ABS(SUMPRODUCT(CODE(MID(Table1[[#This Row],[naam]],ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))),1))*(ROW(INDIRECT("1:"&amp;LEN(Table1[[#This Row],[naam]]))))))), 4))</f>
+        <v>janus-4-d&amp;a-1040</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="I5" s="4"/>
+      <c r="J5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="M5" s="4"/>
+      <c r="N5" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
       <c r="R5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="S5" s="5"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>